--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="154">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -408,26 +408,13 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.identifiantVaccinRecommande</t>
-  </si>
-  <si>
-    <t>fr-lm-immunization-recommendation.codeVaccinRecommande</t>
+    <t>fr-lm-immunization-recommendation.recommendedVaccineCode</t>
   </si>
   <si>
     <t>Type d'acte : vaccination</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.descriptionNarrativeVaccinRecommande</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Partie narrative de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-immunization-recommendation.statutVaccinRecommande</t>
+    <t>fr-lm-immunization-recommendation.recommendedVaccineStatus</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -437,19 +424,19 @@
     <t>Statut de l’entrée</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.periodeVaccination</t>
+    <t>fr-lm-immunization-recommendation.vaccinationPeriod</t>
   </si>
   <si>
     <t>Période de vaccination souhaitable</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.voieAdministration</t>
+    <t>fr-lm-immunization-recommendation.routeOfAdministration</t>
   </si>
   <si>
     <t>Voie d’administration</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.regionAnatomique</t>
+    <t>fr-lm-immunization-recommendation.anatomicalRegion</t>
   </si>
   <si>
     <t>Région anatomique d'administration</t>
@@ -458,7 +445,7 @@
     <t>SNOMED CT (2.16.840.1.113883.6.96)</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.doseAdministree</t>
+    <t>fr-lm-immunization-recommendation.administeredDose</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity
@@ -468,7 +455,7 @@
     <t>Dose administrée</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.vaccin</t>
+    <t>fr-lm-immunization-recommendation.vaccine</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication
@@ -478,7 +465,7 @@
     <t>Vaccin</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.prescription</t>
+    <t>fr-lm-immunization-recommendation.prescriptionReference</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prescription-entree
@@ -488,7 +475,7 @@
     <t>Référence de la prescription</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.rangVaccination</t>
+    <t>fr-lm-immunization-recommendation.vaccinationRank</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dose-number
@@ -498,10 +485,10 @@
     <t>Rang de la vaccination</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.commentaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-commentaire-er
+    <t>fr-lm-immunization-recommendation.comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
@@ -807,11 +794,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="62.58203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="62.58203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -841,7 +828,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="62.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="53.02734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2385,13 +2372,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2459,10 +2446,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2485,13 +2472,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2542,7 +2529,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2559,10 +2546,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2585,13 +2572,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2642,7 +2629,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2659,10 +2646,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2670,7 +2657,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2685,7 +2672,7 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>135</v>
@@ -2742,10 +2729,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2770,10 +2757,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2785,7 +2772,7 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>137</v>
@@ -2821,7 +2808,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2845,10 +2832,10 @@
         <v>136</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2859,10 +2846,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2885,13 +2872,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2942,7 +2929,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2959,10 +2946,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2970,10 +2957,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -2985,13 +2972,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3021,34 +3008,34 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
@@ -3059,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3085,13 +3072,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3142,7 +3129,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3159,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3170,7 +3157,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3185,13 +3172,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3242,10 +3229,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3259,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3285,13 +3272,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3342,7 +3329,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3354,206 +3341,6 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q27" s="2"/>
-      <c r="R27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-immunization-recommendation.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-immunization-recommendation.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-immunization-recommendation.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-immunization-recommendation.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -807,7 +811,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1772,13 +1776,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1829,7 +1833,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1846,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1872,13 +1876,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1929,7 +1933,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1946,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1972,13 +1976,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2029,7 +2033,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2046,10 +2050,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2072,13 +2076,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2129,7 +2133,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2146,10 +2150,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2172,13 +2176,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2229,7 +2233,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2246,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2272,13 +2276,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2329,7 +2333,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2346,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2372,13 +2376,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2429,7 +2433,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2446,10 +2450,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2472,13 +2476,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2529,7 +2533,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2546,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2572,13 +2576,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2629,7 +2633,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2646,10 +2650,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2672,13 +2676,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2729,7 +2733,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2746,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2772,13 +2776,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2808,7 +2812,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2829,7 +2833,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2846,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2872,13 +2876,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2929,7 +2933,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2946,10 +2950,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2972,13 +2976,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3029,7 +3033,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3046,10 +3050,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3072,13 +3076,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3129,7 +3133,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3146,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3172,13 +3176,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3229,7 +3233,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3246,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3272,13 +3276,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3329,7 +3333,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-immunization-recommendation.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-immunization-recommendation.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-immunization-recommendation.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-immunization-recommendation.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-immunization-recommendation.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-immunization-recommendation.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-immunization-recommendation.header.source</t>
+    <t>fr-lm-immunization-recommendation.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-immunization-recommendation.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -798,11 +840,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ25"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="59.546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.2578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="66.2578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -811,7 +853,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.88671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -825,8 +867,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="31.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1576,13 +1618,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1633,7 +1675,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1650,10 +1692,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1676,13 +1718,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1733,7 +1775,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1750,10 +1792,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1776,13 +1818,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1833,7 +1875,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1850,10 +1892,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1876,7 +1918,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1976,13 +2018,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2033,7 +2075,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2050,10 +2092,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2064,7 +2106,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2076,13 +2118,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2133,13 +2175,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2150,10 +2192,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2164,7 +2206,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2176,13 +2218,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2233,13 +2275,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2250,10 +2292,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2264,7 +2306,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2276,13 +2318,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2333,13 +2375,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2350,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2361,7 +2403,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2376,13 +2418,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2433,10 +2475,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2512,10 +2554,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2533,7 +2575,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2550,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2561,7 +2603,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2576,13 +2618,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2633,10 +2675,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2650,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2676,13 +2718,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2733,7 +2775,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2750,10 +2792,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2761,10 +2803,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2776,13 +2818,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2812,7 +2854,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2833,13 +2875,13 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2850,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2861,7 +2903,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2876,13 +2918,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2933,10 +2975,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2950,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2976,13 +3018,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3033,7 +3075,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3050,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3076,13 +3118,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3133,7 +3175,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3150,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3164,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3176,13 +3218,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3212,7 +3254,7 @@
         <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -3233,13 +3275,13 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
@@ -3250,10 +3292,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3276,13 +3318,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3333,7 +3375,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3345,6 +3387,406 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-immunization-recommendation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
